--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/72.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/72.xlsx
@@ -426,13 +426,13 @@
         <v>-1.88816154033855</v>
       </c>
       <c r="E2">
-        <v>-6.691596792095867</v>
+        <v>-2.746734400638034</v>
       </c>
       <c r="F2">
-        <v>-2.599682963168655</v>
+        <v>-1.513908673623231</v>
       </c>
       <c r="G2">
-        <v>-11.36423742316425</v>
+        <v>-7.961079108127454</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.289952837095015</v>
       </c>
       <c r="E3">
-        <v>-6.447946776587171</v>
+        <v>-4.077363089155861</v>
       </c>
       <c r="F3">
-        <v>-2.420191485962655</v>
+        <v>-1.217180843001226</v>
       </c>
       <c r="G3">
-        <v>-11.50220950851735</v>
+        <v>-8.535466785772931</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.850029279278154</v>
       </c>
       <c r="E4">
-        <v>-7.439496916832665</v>
+        <v>-3.977944970791466</v>
       </c>
       <c r="F4">
-        <v>-2.673748949387764</v>
+        <v>-1.28760863958724</v>
       </c>
       <c r="G4">
-        <v>-11.62492063239746</v>
+        <v>-8.14990356520882</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.6349823897372373</v>
       </c>
       <c r="E5">
-        <v>-7.697887115236328</v>
+        <v>-5.37599358033549</v>
       </c>
       <c r="F5">
-        <v>-2.587519216225947</v>
+        <v>-1.29213898091315</v>
       </c>
       <c r="G5">
-        <v>-11.24593626106003</v>
+        <v>-7.877795142505629</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.5837054511514549</v>
       </c>
       <c r="E6">
-        <v>-8.177348357746443</v>
+        <v>-5.919596128690247</v>
       </c>
       <c r="F6">
-        <v>-2.282651847504034</v>
+        <v>-1.218470611047385</v>
       </c>
       <c r="G6">
-        <v>-11.45492054340263</v>
+        <v>-7.143520100711531</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.6512547695805487</v>
       </c>
       <c r="E7">
-        <v>-9.416642254003566</v>
+        <v>-7.105331762858653</v>
       </c>
       <c r="F7">
-        <v>-2.402770919481782</v>
+        <v>-1.533292470848739</v>
       </c>
       <c r="G7">
-        <v>-11.8669435346221</v>
+        <v>-7.432943529583912</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.7709355159285546</v>
       </c>
       <c r="E8">
-        <v>-9.605742271615865</v>
+        <v>-7.421650200768435</v>
       </c>
       <c r="F8">
-        <v>-2.395354546124518</v>
+        <v>-0.831294172081104</v>
       </c>
       <c r="G8">
-        <v>-12.17906973546428</v>
+        <v>-7.849035235537096</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.884362789568636</v>
       </c>
       <c r="E9">
-        <v>-11.18477134487643</v>
+        <v>-8.518799826398794</v>
       </c>
       <c r="F9">
-        <v>-2.040950806715194</v>
+        <v>-1.240591334171742</v>
       </c>
       <c r="G9">
-        <v>-11.45987518795739</v>
+        <v>-7.79665709578368</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.9336496027323778</v>
       </c>
       <c r="E10">
-        <v>-11.07645930356097</v>
+        <v>-8.611936951314551</v>
       </c>
       <c r="F10">
-        <v>-2.257067720268571</v>
+        <v>-1.177555888288311</v>
       </c>
       <c r="G10">
-        <v>-11.60738250316223</v>
+        <v>-7.508615061187825</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.8750596724668857</v>
       </c>
       <c r="E11">
-        <v>-10.98047376849439</v>
+        <v>-9.540446204899265</v>
       </c>
       <c r="F11">
-        <v>-1.791717421132698</v>
+        <v>-0.7848028799663845</v>
       </c>
       <c r="G11">
-        <v>-10.50836031037714</v>
+        <v>-6.668235157825964</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.6787397556572202</v>
       </c>
       <c r="E12">
-        <v>-12.57984474699742</v>
+        <v>-10.28821500388984</v>
       </c>
       <c r="F12">
-        <v>-1.753261292825134</v>
+        <v>-0.72945385521353</v>
       </c>
       <c r="G12">
-        <v>-10.45980807496203</v>
+        <v>-6.590913171777649</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.3369969333016273</v>
       </c>
       <c r="E13">
-        <v>-12.38527433278385</v>
+        <v>-11.09078739532124</v>
       </c>
       <c r="F13">
-        <v>-1.441250911988881</v>
+        <v>-0.3038196312048796</v>
       </c>
       <c r="G13">
-        <v>-9.922124141680506</v>
+        <v>-6.699190202017766</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.1338998250495422</v>
       </c>
       <c r="E14">
-        <v>-13.34600820740715</v>
+        <v>-11.64053508290441</v>
       </c>
       <c r="F14">
-        <v>-1.382390437815559</v>
+        <v>-0.1421852701010289</v>
       </c>
       <c r="G14">
-        <v>-9.940039611395074</v>
+        <v>-5.335199524642835</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.6981103892229256</v>
       </c>
       <c r="E15">
-        <v>-14.2167975312901</v>
+        <v>-12.50954924497635</v>
       </c>
       <c r="F15">
-        <v>-1.068518715425215</v>
+        <v>0.5702819359031867</v>
       </c>
       <c r="G15">
-        <v>-8.939555783261666</v>
+        <v>-6.553845211820602</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.306158518039932</v>
       </c>
       <c r="E16">
-        <v>-14.75711693598929</v>
+        <v>-12.78550086558176</v>
       </c>
       <c r="F16">
-        <v>-0.8025986968807264</v>
+        <v>0.08598273242827534</v>
       </c>
       <c r="G16">
-        <v>-8.746843078632359</v>
+        <v>-5.661950129975459</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.903504825445341</v>
       </c>
       <c r="E17">
-        <v>-15.25563852559769</v>
+        <v>-14.05352340094354</v>
       </c>
       <c r="F17">
-        <v>-0.6213096624106518</v>
+        <v>0.7755364677036538</v>
       </c>
       <c r="G17">
-        <v>-8.110896403310141</v>
+        <v>-4.100433195943515</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.433422070719355</v>
       </c>
       <c r="E18">
-        <v>-16.16881436619244</v>
+        <v>-15.23371618292656</v>
       </c>
       <c r="F18">
-        <v>-0.1253545012109485</v>
+        <v>1.002277193197934</v>
       </c>
       <c r="G18">
-        <v>-8.279574160016516</v>
+        <v>-4.411696435515561</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.841514883038477</v>
       </c>
       <c r="E19">
-        <v>-16.60569436760843</v>
+        <v>-17.06724549541821</v>
       </c>
       <c r="F19">
-        <v>0.395847641691278</v>
+        <v>1.248118414265966</v>
       </c>
       <c r="G19">
-        <v>-7.393102937409134</v>
+        <v>-3.20181160990151</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.082461148998542</v>
       </c>
       <c r="E20">
-        <v>-17.90043037114146</v>
+        <v>-17.56170504384172</v>
       </c>
       <c r="F20">
-        <v>0.7589210743383014</v>
+        <v>1.62192417498366</v>
       </c>
       <c r="G20">
-        <v>-6.977119511767412</v>
+        <v>-2.660396927706894</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.128062035307336</v>
       </c>
       <c r="E21">
-        <v>-18.94440665497375</v>
+        <v>-18.0081401254139</v>
       </c>
       <c r="F21">
-        <v>1.277096362750698</v>
+        <v>1.75755774004844</v>
       </c>
       <c r="G21">
-        <v>-7.030931545342304</v>
+        <v>-3.517346999943952</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.972326322627555</v>
       </c>
       <c r="E22">
-        <v>-18.97265074735959</v>
+        <v>-17.14752628262618</v>
       </c>
       <c r="F22">
-        <v>1.125278155370022</v>
+        <v>2.155427573817459</v>
       </c>
       <c r="G22">
-        <v>-6.490235450669207</v>
+        <v>-3.583073149001189</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.632439768010172</v>
       </c>
       <c r="E23">
-        <v>-20.65381955186317</v>
+        <v>-17.51610783905849</v>
       </c>
       <c r="F23">
-        <v>1.261766595594491</v>
+        <v>2.583819432910029</v>
       </c>
       <c r="G23">
-        <v>-6.808786283324778</v>
+        <v>-3.821486707510442</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.146575587001919</v>
       </c>
       <c r="E24">
-        <v>-21.16397931967128</v>
+        <v>-19.64354417159596</v>
       </c>
       <c r="F24">
-        <v>1.722960147103116</v>
+        <v>2.006868163799396</v>
       </c>
       <c r="G24">
-        <v>-6.812526875902545</v>
+        <v>-3.383614252845664</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.568826468447896</v>
       </c>
       <c r="E25">
-        <v>-20.63641662625169</v>
+        <v>-18.5141019978169</v>
       </c>
       <c r="F25">
-        <v>1.656359407918035</v>
+        <v>2.960782930167194</v>
       </c>
       <c r="G25">
-        <v>-7.11102616360835</v>
+        <v>-2.641342874111199</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.9604767828683609</v>
       </c>
       <c r="E26">
-        <v>-20.53299986533852</v>
+        <v>-19.33397768843161</v>
       </c>
       <c r="F26">
-        <v>1.766750961484709</v>
+        <v>3.509248301030358</v>
       </c>
       <c r="G26">
-        <v>-6.86786795872414</v>
+        <v>-3.417154899626307</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3821164755537581</v>
       </c>
       <c r="E27">
-        <v>-21.28684587644739</v>
+        <v>-19.73682620767996</v>
       </c>
       <c r="F27">
-        <v>1.568086920740914</v>
+        <v>2.66855313454239</v>
       </c>
       <c r="G27">
-        <v>-7.037073992101585</v>
+        <v>-3.446587457014527</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1134306230227163</v>
       </c>
       <c r="E28">
-        <v>-21.38908523411856</v>
+        <v>-19.20499316327114</v>
       </c>
       <c r="F28">
-        <v>1.587141027740109</v>
+        <v>2.647381720461641</v>
       </c>
       <c r="G28">
-        <v>-6.6946161791639</v>
+        <v>-4.143463135474073</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4870547654555748</v>
       </c>
       <c r="E29">
-        <v>-20.91332375487272</v>
+        <v>-19.33764575237782</v>
       </c>
       <c r="F29">
-        <v>1.900585312550608</v>
+        <v>2.667719796935174</v>
       </c>
       <c r="G29">
-        <v>-7.064068601871137</v>
+        <v>-4.333294927574189</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7168017962849222</v>
       </c>
       <c r="E30">
-        <v>-20.45677659084141</v>
+        <v>-19.1193687767341</v>
       </c>
       <c r="F30">
-        <v>1.586808024044183</v>
+        <v>2.497279890339565</v>
       </c>
       <c r="G30">
-        <v>-7.28085234786053</v>
+        <v>-3.132646740649975</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7961941106241701</v>
       </c>
       <c r="E31">
-        <v>-20.84488492719479</v>
+        <v>-19.80191849306621</v>
       </c>
       <c r="F31">
-        <v>1.734366766239665</v>
+        <v>2.296674156403608</v>
       </c>
       <c r="G31">
-        <v>-7.445612326024928</v>
+        <v>-3.545430975271239</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7348423291049113</v>
       </c>
       <c r="E32">
-        <v>-20.32462213387557</v>
+        <v>-18.94996762105517</v>
       </c>
       <c r="F32">
-        <v>1.393689074694729</v>
+        <v>2.44390155163797</v>
       </c>
       <c r="G32">
-        <v>-7.418962244519117</v>
+        <v>-2.888415576315826</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5572159989875827</v>
       </c>
       <c r="E33">
-        <v>-19.68708997765371</v>
+        <v>-18.97989177729786</v>
       </c>
       <c r="F33">
-        <v>1.530999255382775</v>
+        <v>2.438276936972962</v>
       </c>
       <c r="G33">
-        <v>-7.611638855711271</v>
+        <v>-3.887242387561714</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.3019234329479186</v>
       </c>
       <c r="E34">
-        <v>-19.76389742529781</v>
+        <v>-18.00308634842134</v>
       </c>
       <c r="F34">
-        <v>1.243052119230444</v>
+        <v>2.511582481916301</v>
       </c>
       <c r="G34">
-        <v>-7.390914362628984</v>
+        <v>-4.107897974991253</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.01455876283970827</v>
       </c>
       <c r="E35">
-        <v>-19.92852556937266</v>
+        <v>-17.21275895070668</v>
       </c>
       <c r="F35">
-        <v>1.488797249679751</v>
+        <v>2.272639904578783</v>
       </c>
       <c r="G35">
-        <v>-6.859386000992975</v>
+        <v>-4.396914532390261</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.2547365595245157</v>
       </c>
       <c r="E36">
-        <v>-19.64838511031015</v>
+        <v>-17.57647239758074</v>
       </c>
       <c r="F36">
-        <v>1.500800293346316</v>
+        <v>2.425899471240331</v>
       </c>
       <c r="G36">
-        <v>-6.893704297283207</v>
+        <v>-3.337611526582249</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.4593050276154894</v>
       </c>
       <c r="E37">
-        <v>-19.03230433546263</v>
+        <v>-18.41973765644506</v>
       </c>
       <c r="F37">
-        <v>1.478303491421087</v>
+        <v>2.752339183865949</v>
       </c>
       <c r="G37">
-        <v>-6.739664069953516</v>
+        <v>-3.592408224337809</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.5602712834498758</v>
       </c>
       <c r="E38">
-        <v>-19.08680904861895</v>
+        <v>-18.41832930102868</v>
       </c>
       <c r="F38">
-        <v>1.744494386106292</v>
+        <v>2.288377228497168</v>
       </c>
       <c r="G38">
-        <v>-7.013780600251087</v>
+        <v>-2.809177356876796</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.5308916116162467</v>
       </c>
       <c r="E39">
-        <v>-18.42415744707655</v>
+        <v>-17.15179210514141</v>
       </c>
       <c r="F39">
-        <v>1.441943132642606</v>
+        <v>2.399573955179363</v>
       </c>
       <c r="G39">
-        <v>-6.339696286743443</v>
+        <v>-3.381107399574248</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.357447939640947</v>
       </c>
       <c r="E40">
-        <v>-18.28843002411865</v>
+        <v>-16.02216426392804</v>
       </c>
       <c r="F40">
-        <v>1.554680622694007</v>
+        <v>2.541170108809494</v>
       </c>
       <c r="G40">
-        <v>-6.262252895497428</v>
+        <v>-3.418181921974413</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.04280331356116359</v>
       </c>
       <c r="E41">
-        <v>-18.26387663804907</v>
+        <v>-16.10143520143231</v>
       </c>
       <c r="F41">
-        <v>1.380710214227666</v>
+        <v>2.628935635136101</v>
       </c>
       <c r="G41">
-        <v>-6.326745305248314</v>
+        <v>-3.010496705656526</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3940033330376914</v>
       </c>
       <c r="E42">
-        <v>-17.41546250423802</v>
+        <v>-16.74857225102443</v>
       </c>
       <c r="F42">
-        <v>1.502811569400313</v>
+        <v>2.489125441626406</v>
       </c>
       <c r="G42">
-        <v>-5.931440137874213</v>
+        <v>-2.950302696148513</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.9216705776398916</v>
       </c>
       <c r="E43">
-        <v>-17.42081063204107</v>
+        <v>-15.20703441407337</v>
       </c>
       <c r="F43">
-        <v>1.555442720704583</v>
+        <v>2.572475769696092</v>
       </c>
       <c r="G43">
-        <v>-6.314755721670104</v>
+        <v>-3.159897285701164</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.50388496065903</v>
       </c>
       <c r="E44">
-        <v>-16.80969759317997</v>
+        <v>-15.42671521665947</v>
       </c>
       <c r="F44">
-        <v>1.264384236587337</v>
+        <v>2.148144567612046</v>
       </c>
       <c r="G44">
-        <v>-5.919670396140484</v>
+        <v>-1.313521101986027</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.103694383173427</v>
       </c>
       <c r="E45">
-        <v>-16.11164691031961</v>
+        <v>-14.8769675290763</v>
       </c>
       <c r="F45">
-        <v>1.395438586649441</v>
+        <v>2.311089405947125</v>
       </c>
       <c r="G45">
-        <v>-5.935820568656071</v>
+        <v>-2.141327364332097</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.687304947204647</v>
       </c>
       <c r="E46">
-        <v>-16.56721592396525</v>
+        <v>-15.27771030791108</v>
       </c>
       <c r="F46">
-        <v>1.113268484764235</v>
+        <v>2.335294301456927</v>
       </c>
       <c r="G46">
-        <v>-5.58140598435577</v>
+        <v>-1.521931170555718</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.22873086734146</v>
       </c>
       <c r="E47">
-        <v>-15.94700518082274</v>
+        <v>-14.93167149508896</v>
       </c>
       <c r="F47">
-        <v>1.279394253926064</v>
+        <v>2.575462862550588</v>
       </c>
       <c r="G47">
-        <v>-5.109855071604851</v>
+        <v>-2.037922948107756</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.710264359649726</v>
       </c>
       <c r="E48">
-        <v>-15.79859350216935</v>
+        <v>-14.44375559160652</v>
       </c>
       <c r="F48">
-        <v>1.289526843997108</v>
+        <v>1.713213576241777</v>
       </c>
       <c r="G48">
-        <v>-5.690234259817872</v>
+        <v>-1.242827183487791</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.12463542334696</v>
       </c>
       <c r="E49">
-        <v>-14.99815855046957</v>
+        <v>-13.52663092167709</v>
       </c>
       <c r="F49">
-        <v>1.103883082090516</v>
+        <v>2.281632661103575</v>
       </c>
       <c r="G49">
-        <v>-5.124774786035645</v>
+        <v>-1.810721323667126</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.471427850829403</v>
       </c>
       <c r="E50">
-        <v>-14.61683839665369</v>
+        <v>-10.71850607562467</v>
       </c>
       <c r="F50">
-        <v>0.9762714269544468</v>
+        <v>2.173305399104678</v>
       </c>
       <c r="G50">
-        <v>-5.260689545470965</v>
+        <v>-2.902475610698047</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.755712340932085</v>
       </c>
       <c r="E51">
-        <v>-14.86058803859055</v>
+        <v>-11.50115318142232</v>
       </c>
       <c r="F51">
-        <v>0.9316870366009719</v>
+        <v>2.171254361415346</v>
       </c>
       <c r="G51">
-        <v>-5.379351641946723</v>
+        <v>-1.607091994909546</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.984602558695222</v>
       </c>
       <c r="E52">
-        <v>-13.77739064137783</v>
+        <v>-11.91506929114542</v>
       </c>
       <c r="F52">
-        <v>0.9103632029181069</v>
+        <v>2.048839883364441</v>
       </c>
       <c r="G52">
-        <v>-4.391789264314409</v>
+        <v>-0.8306007565316325</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.167571922195136</v>
       </c>
       <c r="E53">
-        <v>-13.71034658369427</v>
+        <v>-11.82161970152313</v>
       </c>
       <c r="F53">
-        <v>0.8004123408097229</v>
+        <v>2.174508188573543</v>
       </c>
       <c r="G53">
-        <v>-5.317881237252085</v>
+        <v>-1.845413679215135</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.309063944280179</v>
       </c>
       <c r="E54">
-        <v>-13.18867543495866</v>
+        <v>-10.31924863626441</v>
       </c>
       <c r="F54">
-        <v>1.050201560919497</v>
+        <v>1.752970241371736</v>
       </c>
       <c r="G54">
-        <v>-5.142168541522262</v>
+        <v>-1.361036471388346</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.409130674769433</v>
       </c>
       <c r="E55">
-        <v>-12.25362706490687</v>
+        <v>-11.11073985179904</v>
       </c>
       <c r="F55">
-        <v>0.9376164904702107</v>
+        <v>1.758989158920477</v>
       </c>
       <c r="G55">
-        <v>-5.449284317043168</v>
+        <v>-1.864861479397963</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.46435544164931</v>
       </c>
       <c r="E56">
-        <v>-12.83677677677061</v>
+        <v>-9.757237841068468</v>
       </c>
       <c r="F56">
-        <v>1.069273892001553</v>
+        <v>2.209087557436006</v>
       </c>
       <c r="G56">
-        <v>-5.210644354246313</v>
+        <v>-1.959521440166384</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.469609555761656</v>
       </c>
       <c r="E57">
-        <v>-11.82432320050571</v>
+        <v>-10.15544467445895</v>
       </c>
       <c r="F57">
-        <v>0.9206929444310168</v>
+        <v>2.057658682734645</v>
       </c>
       <c r="G57">
-        <v>-5.906952381376077</v>
+        <v>-1.266534009254779</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.418191009055668</v>
       </c>
       <c r="E58">
-        <v>-11.13903828587297</v>
+        <v>-9.653907121161446</v>
       </c>
       <c r="F58">
-        <v>0.9389700428063851</v>
+        <v>1.835709234298156</v>
       </c>
       <c r="G58">
-        <v>-5.452470383177389</v>
+        <v>-2.075637308712014</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.30400100280224</v>
       </c>
       <c r="E59">
-        <v>-10.993819181395</v>
+        <v>-8.679836890585561</v>
       </c>
       <c r="F59">
-        <v>0.9304925308061349</v>
+        <v>2.306700715447094</v>
       </c>
       <c r="G59">
-        <v>-5.770483095497212</v>
+        <v>-2.579557472146855</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.124507466986425</v>
       </c>
       <c r="E60">
-        <v>-11.78587645618059</v>
+        <v>-8.327286132140408</v>
       </c>
       <c r="F60">
-        <v>0.7121763017983253</v>
+        <v>2.021266845994857</v>
       </c>
       <c r="G60">
-        <v>-6.124293935030575</v>
+        <v>-1.756810853445449</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.882127752922281</v>
       </c>
       <c r="E61">
-        <v>-11.29543366420187</v>
+        <v>-7.521417011631422</v>
       </c>
       <c r="F61">
-        <v>1.026538417691126</v>
+        <v>2.224496847862882</v>
       </c>
       <c r="G61">
-        <v>-6.006255270651112</v>
+        <v>-3.06147376380406</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.584147820199877</v>
       </c>
       <c r="E62">
-        <v>-11.57937351295681</v>
+        <v>-8.691574695213442</v>
       </c>
       <c r="F62">
-        <v>1.018233206110658</v>
+        <v>2.317703091291077</v>
       </c>
       <c r="G62">
-        <v>-5.633380533857373</v>
+        <v>-3.21818490548314</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.242074161517638</v>
       </c>
       <c r="E63">
-        <v>-10.61034800242547</v>
+        <v>-6.556036922676254</v>
       </c>
       <c r="F63">
-        <v>0.795544853950873</v>
+        <v>1.786058548909159</v>
       </c>
       <c r="G63">
-        <v>-6.624732722390846</v>
+        <v>-3.395593992759196</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.870853470481621</v>
       </c>
       <c r="E64">
-        <v>-10.22845273241061</v>
+        <v>-7.871160116191819</v>
       </c>
       <c r="F64">
-        <v>0.9057508532193193</v>
+        <v>1.733960866212293</v>
       </c>
       <c r="G64">
-        <v>-6.852761214664456</v>
+        <v>-4.825852220748672</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.488157432375266</v>
       </c>
       <c r="E65">
-        <v>-10.25671041021848</v>
+        <v>-8.520661029215947</v>
       </c>
       <c r="F65">
-        <v>0.8044779680226629</v>
+        <v>1.628266155819493</v>
       </c>
       <c r="G65">
-        <v>-7.149045677817636</v>
+        <v>-4.723612638177935</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.11091482089215</v>
       </c>
       <c r="E66">
-        <v>-9.487902320988267</v>
+        <v>-7.745734971601372</v>
       </c>
       <c r="F66">
-        <v>0.9074904247651983</v>
+        <v>1.616437069307516</v>
       </c>
       <c r="G66">
-        <v>-7.171098767918664</v>
+        <v>-3.89872994424133</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.754085928132103</v>
       </c>
       <c r="E67">
-        <v>-9.495881492189781</v>
+        <v>-7.589760741355183</v>
       </c>
       <c r="F67">
-        <v>1.005691723632274</v>
+        <v>1.923559254099849</v>
       </c>
       <c r="G67">
-        <v>-7.241628625338928</v>
+        <v>-5.028730149769139</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.429349068176483</v>
       </c>
       <c r="E68">
-        <v>-8.996218727131449</v>
+        <v>-8.145793950860995</v>
       </c>
       <c r="F68">
-        <v>0.9897423376587724</v>
+        <v>1.629039850973708</v>
       </c>
       <c r="G68">
-        <v>-7.552297963808713</v>
+        <v>-4.347978394052704</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.147222909424408</v>
       </c>
       <c r="E69">
-        <v>-10.29659268080403</v>
+        <v>-7.174241551833373</v>
       </c>
       <c r="F69">
-        <v>0.8330367626015787</v>
+        <v>1.968914026137928</v>
       </c>
       <c r="G69">
-        <v>-7.116138306797965</v>
+        <v>-5.672876597768409</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.913686991981764</v>
       </c>
       <c r="E70">
-        <v>-10.00961875446395</v>
+        <v>-7.373974426415682</v>
       </c>
       <c r="F70">
-        <v>0.9687283133845545</v>
+        <v>1.411119581584436</v>
       </c>
       <c r="G70">
-        <v>-7.357035750027718</v>
+        <v>-4.77351017443241</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.729926037132533</v>
       </c>
       <c r="E71">
-        <v>-9.831441416158155</v>
+        <v>-7.742963545508679</v>
       </c>
       <c r="F71">
-        <v>0.7812853374790824</v>
+        <v>1.602934680641884</v>
       </c>
       <c r="G71">
-        <v>-7.923164593008071</v>
+        <v>-5.332968293982413</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.592905688433009</v>
       </c>
       <c r="E72">
-        <v>-9.795331364420992</v>
+        <v>-7.958527965221803</v>
       </c>
       <c r="F72">
-        <v>0.628069674289883</v>
+        <v>1.624911267838155</v>
       </c>
       <c r="G72">
-        <v>-7.744728483383908</v>
+        <v>-5.701442912664935</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.500195440588724</v>
       </c>
       <c r="E73">
-        <v>-10.21581376145521</v>
+        <v>-7.241987522988122</v>
       </c>
       <c r="F73">
-        <v>0.5044731159551827</v>
+        <v>1.665393582812967</v>
       </c>
       <c r="G73">
-        <v>-7.674920494706722</v>
+        <v>-5.391298569644661</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.448407252329353</v>
       </c>
       <c r="E74">
-        <v>-9.903118102751561</v>
+        <v>-7.517219116226311</v>
       </c>
       <c r="F74">
-        <v>0.5488181081292487</v>
+        <v>1.523711278972945</v>
       </c>
       <c r="G74">
-        <v>-7.457615034489376</v>
+        <v>-4.205845719762237</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.433182850639678</v>
       </c>
       <c r="E75">
-        <v>-10.15682133055729</v>
+        <v>-7.837151276394214</v>
       </c>
       <c r="F75">
-        <v>0.7300789781076281</v>
+        <v>1.253081991743541</v>
       </c>
       <c r="G75">
-        <v>-7.137718900994432</v>
+        <v>-4.28778110332313</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.449328277294374</v>
       </c>
       <c r="E76">
-        <v>-10.80712378348077</v>
+        <v>-8.668615331994554</v>
       </c>
       <c r="F76">
-        <v>0.4868868759937492</v>
+        <v>0.9847472822198914</v>
       </c>
       <c r="G76">
-        <v>-7.255872408128478</v>
+        <v>-5.50103574347873</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.493142680117353</v>
       </c>
       <c r="E77">
-        <v>-10.77422441981505</v>
+        <v>-9.090827606099699</v>
       </c>
       <c r="F77">
-        <v>0.3363360707393559</v>
+        <v>1.426613365486398</v>
       </c>
       <c r="G77">
-        <v>-7.251590413993402</v>
+        <v>-4.852735268985203</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.559826298236846</v>
       </c>
       <c r="E78">
-        <v>-11.01393466293707</v>
+        <v>-9.230635184138507</v>
       </c>
       <c r="F78">
-        <v>0.2703798013936537</v>
+        <v>1.117325828303147</v>
       </c>
       <c r="G78">
-        <v>-7.03503307229161</v>
+        <v>-4.825648785011986</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.642198838275439</v>
       </c>
       <c r="E79">
-        <v>-11.58689530828355</v>
+        <v>-8.957717641118236</v>
       </c>
       <c r="F79">
-        <v>0.2840892819099855</v>
+        <v>1.04599179777847</v>
       </c>
       <c r="G79">
-        <v>-6.85575696994823</v>
+        <v>-4.689399340977604</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.731432897806911</v>
       </c>
       <c r="E80">
-        <v>-13.44914420293184</v>
+        <v>-9.666740816499184</v>
       </c>
       <c r="F80">
-        <v>0.3352252300522018</v>
+        <v>1.073251712269796</v>
       </c>
       <c r="G80">
-        <v>-6.879831292529875</v>
+        <v>-4.149270897634291</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.819160537420293</v>
       </c>
       <c r="E81">
-        <v>-12.6001458959738</v>
+        <v>-10.07346118102409</v>
       </c>
       <c r="F81">
-        <v>0.1733407019927056</v>
+        <v>0.6650537937226725</v>
       </c>
       <c r="G81">
-        <v>-6.504315172380784</v>
+        <v>-4.85600336565841</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.898307600653538</v>
       </c>
       <c r="E82">
-        <v>-12.8545419803027</v>
+        <v>-10.4353722952431</v>
       </c>
       <c r="F82">
-        <v>0.08653276838373421</v>
+        <v>0.7711278963859548</v>
       </c>
       <c r="G82">
-        <v>-6.009795708713752</v>
+        <v>-3.742914576047979</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.962942257444355</v>
       </c>
       <c r="E83">
-        <v>-13.08376880609697</v>
+        <v>-12.65747637691091</v>
       </c>
       <c r="F83">
-        <v>-0.1821009817723259</v>
+        <v>0.6542137778896382</v>
       </c>
       <c r="G83">
-        <v>-6.610003318810499</v>
+        <v>-4.096859945665281</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.009587576034643</v>
       </c>
       <c r="E84">
-        <v>-14.97538032621099</v>
+        <v>-12.2273121024483</v>
       </c>
       <c r="F84">
-        <v>-0.04977757284913285</v>
+        <v>0.7729734989593922</v>
       </c>
       <c r="G84">
-        <v>-6.25988057230995</v>
+        <v>-4.103970352784597</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.038478987774591</v>
       </c>
       <c r="E85">
-        <v>-15.70628055952299</v>
+        <v>-13.04910333756825</v>
       </c>
       <c r="F85">
-        <v>-0.2217010854631562</v>
+        <v>0.7443931668280036</v>
       </c>
       <c r="G85">
-        <v>-6.420010746853971</v>
+        <v>-4.305138765372593</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.055716246752223</v>
       </c>
       <c r="E86">
-        <v>-16.32994652833336</v>
+        <v>-14.29707831849808</v>
       </c>
       <c r="F86">
-        <v>-0.0139921010481942</v>
+        <v>0.4380786402533996</v>
       </c>
       <c r="G86">
-        <v>-5.990643218471273</v>
+        <v>-3.41702365076393</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.071109959957718</v>
       </c>
       <c r="E87">
-        <v>-17.51194617144544</v>
+        <v>-15.64392347243737</v>
       </c>
       <c r="F87">
-        <v>-0.3845854529778314</v>
+        <v>0.5234551549903335</v>
       </c>
       <c r="G87">
-        <v>-5.57289121440901</v>
+        <v>-3.518465896495723</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.095229258089191</v>
       </c>
       <c r="E88">
-        <v>-18.56744742162726</v>
+        <v>-16.87771074430117</v>
       </c>
       <c r="F88">
-        <v>-0.4602924350218867</v>
+        <v>0.439713009139123</v>
       </c>
       <c r="G88">
-        <v>-5.752597156776678</v>
+        <v>-3.015241352031484</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.137346369676549</v>
       </c>
       <c r="E89">
-        <v>-20.00386579143827</v>
+        <v>-19.27197835079259</v>
       </c>
       <c r="F89">
-        <v>-0.8829519916870839</v>
+        <v>0.561121020795627</v>
       </c>
       <c r="G89">
-        <v>-5.837469233633275</v>
+        <v>-3.153384060905666</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.205263801288134</v>
       </c>
       <c r="E90">
-        <v>-21.33433598336583</v>
+        <v>-19.93868746504587</v>
       </c>
       <c r="F90">
-        <v>-0.5029699236141172</v>
+        <v>0.778675980160264</v>
       </c>
       <c r="G90">
-        <v>-6.199811249221196</v>
+        <v>-3.890205330629893</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.305320592423932</v>
       </c>
       <c r="E91">
-        <v>-23.15364588747339</v>
+        <v>-20.3582324679605</v>
       </c>
       <c r="F91">
-        <v>-0.7243834183409942</v>
+        <v>0.2743095763525346</v>
       </c>
       <c r="G91">
-        <v>-5.479104058575402</v>
+        <v>-3.885063656446243</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.43972074947161</v>
       </c>
       <c r="E92">
-        <v>-25.44324234575152</v>
+        <v>-23.81213129292874</v>
       </c>
       <c r="F92">
-        <v>-0.8288977051848051</v>
+        <v>-0.3371746730460045</v>
       </c>
       <c r="G92">
-        <v>-6.167907931998715</v>
+        <v>-3.220386605149527</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.606763476855645</v>
       </c>
       <c r="E93">
-        <v>-26.8878481965684</v>
+        <v>-26.66376571724685</v>
       </c>
       <c r="F93">
-        <v>-1.064025650632431</v>
+        <v>0.01979783367940043</v>
       </c>
       <c r="G93">
-        <v>-5.662222471364893</v>
+        <v>-3.482280585138166</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.800467588957194</v>
       </c>
       <c r="E94">
-        <v>-28.58063706537566</v>
+        <v>-28.42951283079168</v>
       </c>
       <c r="F94">
-        <v>-0.9862999372277531</v>
+        <v>-0.2190362275283502</v>
       </c>
       <c r="G94">
-        <v>-6.047158978611149</v>
+        <v>-3.509787065470991</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.012803944006093</v>
       </c>
       <c r="E95">
-        <v>-30.83093995468924</v>
+        <v>-31.87679555523471</v>
       </c>
       <c r="F95">
-        <v>-1.06581575258988</v>
+        <v>-0.4621388659627267</v>
       </c>
       <c r="G95">
-        <v>-6.154950388060468</v>
+        <v>-4.077054492332472</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.230478954435161</v>
       </c>
       <c r="E96">
-        <v>-33.33429397155143</v>
+        <v>-32.90208282683735</v>
       </c>
       <c r="F96">
-        <v>-1.303588675154645</v>
+        <v>-0.4904458368511914</v>
       </c>
       <c r="G96">
-        <v>-6.024492300078506</v>
+        <v>-4.515799751932063</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.439636175064569</v>
       </c>
       <c r="E97">
-        <v>-35.46824677818594</v>
+        <v>-35.06456501972018</v>
       </c>
       <c r="F97">
-        <v>-1.268204133176661</v>
+        <v>-0.7889803367787025</v>
       </c>
       <c r="G97">
-        <v>-6.258164493434361</v>
+        <v>-4.793200785010638</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.624460328760053</v>
       </c>
       <c r="E98">
-        <v>-38.40149336107029</v>
+        <v>-37.3109394578321</v>
       </c>
       <c r="F98">
-        <v>-1.372088860794344</v>
+        <v>-0.6252038175712122</v>
       </c>
       <c r="G98">
-        <v>-6.564896366032812</v>
+        <v>-4.263929903807527</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.776612056029189</v>
       </c>
       <c r="E99">
-        <v>-40.4999157606406</v>
+        <v>-40.85339032778332</v>
       </c>
       <c r="F99">
-        <v>-1.741434691415366</v>
+        <v>-1.061422920252835</v>
       </c>
       <c r="G99">
-        <v>-6.878581147115727</v>
+        <v>-4.691240106272453</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.884174480203695</v>
       </c>
       <c r="E100">
-        <v>-43.53515716359972</v>
+        <v>-43.10372718065196</v>
       </c>
       <c r="F100">
-        <v>-1.844331176721509</v>
+        <v>-1.124044182434866</v>
       </c>
       <c r="G100">
-        <v>-7.144015565167007</v>
+        <v>-4.822387250781898</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.947266234447961</v>
       </c>
       <c r="E101">
-        <v>-46.17054789710356</v>
+        <v>-45.09856526577083</v>
       </c>
       <c r="F101">
-        <v>-1.556473504248681</v>
+        <v>-1.281721432455543</v>
       </c>
       <c r="G101">
-        <v>-7.068960903216269</v>
+        <v>-5.402064257581199</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.952723309304726</v>
       </c>
       <c r="E102">
-        <v>-49.01919579281362</v>
+        <v>-48.6324833585731</v>
       </c>
       <c r="F102">
-        <v>-1.888997575447861</v>
+        <v>-1.647632851824558</v>
       </c>
       <c r="G102">
-        <v>-7.530966742450763</v>
+        <v>-4.559968275343748</v>
       </c>
     </row>
   </sheetData>
